--- a/pmu-admissions-audit/deliverables_360/02_PMU_Admissions_Content_Review_Register_EN.xlsx
+++ b/pmu-admissions-audit/deliverables_360/02_PMU_Admissions_Content_Review_Register_EN.xlsx
@@ -593,7 +593,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Prepared for management review. Not an approval, publication confirmation or closure certificate.</t>
+          <t>Prepared for Management Review. Not an approval, publication confirmation or closure certificate.</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ready for management review (draft, not approved)</t>
+          <t>Prepared for Management Review (not approved)</t>
         </is>
       </c>
     </row>
